--- a/HCVData/subtyping-comparison/11-report-subtype-agreement/NS5B_CometFullSeqSubtype_1L_Subtyping_Distances.xlsx
+++ b/HCVData/subtyping-comparison/11-report-subtype-agreement/NS5B_CometFullSeqSubtype_1L_Subtyping_Distances.xlsx
@@ -9,13 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Genotype" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_3" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_4" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_5" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_7" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_8" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -575,7 +568,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MN895099</t>
+          <t>MT151093</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,47 +578,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>314</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.750</t>
+          <t>16.887</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>28.044</t>
+          <t>33.459</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31.988</t>
+          <t>34.921</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28.939</t>
+          <t>29.968</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>28.527</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>32.877</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>31.373</t>
+          <t>29.470</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>27.376</t>
+          <t>28.352</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -635,7 +618,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>13.750</t>
+          <t>16.887</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -645,14 +628,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>28.527</t>
+          <t>29.470</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MT151093</t>
+          <t>MK962423</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -662,37 +645,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>357</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16.887</t>
+          <t>15.686</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33.459</t>
+          <t>30.387</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>34.921</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>29.968</t>
+          <t>30.303</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>29.470</t>
+          <t>26.257</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>31.476</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>32.390</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>28.352</t>
+          <t>26.217</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -702,7 +690,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>16.887</t>
+          <t>15.686</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -712,14 +700,14 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>29.470</t>
+          <t>26.257</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MK962423</t>
+          <t>EF115981</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -729,42 +717,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>340</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15.686</t>
+          <t>11.504</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30.387</t>
+          <t>29.389</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30.303</t>
+          <t>31.269</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>30.000</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>26.257</t>
+          <t>29.766</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>31.476</t>
+          <t>31.889</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>32.390</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>26.217</t>
+          <t>31.871</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -774,7 +762,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>15.686</t>
+          <t>11.504</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -784,14 +772,14 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>26.257</t>
+          <t>29.766</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EF115981</t>
+          <t>EF115985</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -806,37 +794,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11.504</t>
+          <t>15.882</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29.389</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>31.269</t>
+          <t>31.579</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>30.000</t>
+          <t>29.553</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>29.766</t>
+          <t>31.090</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>31.889</t>
+          <t>34.062</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>31.871</t>
+          <t>33.123</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>29.435</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -846,24 +834,24 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>11.504</t>
+          <t>15.882</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>29.766</t>
+          <t>29.553</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EF115985</t>
+          <t>OR477052</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -873,42 +861,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>317</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15.882</t>
+          <t>14.734</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>31.579</t>
+          <t>27.891</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30.816</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>29.553</t>
+          <t>31.003</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>31.090</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>34.062</t>
+          <t>26.250</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.123</t>
+          <t>32.667</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>29.435</t>
+          <t>29.787</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -918,24 +906,24 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>15.882</t>
+          <t>14.734</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>29.553</t>
+          <t>26.250</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OR477052</t>
+          <t>OR520348</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -945,42 +933,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>338</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>14.734</t>
+          <t>14.201</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27.891</t>
+          <t>31.058</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30.816</t>
+          <t>34.242</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>31.003</t>
+          <t>29.814</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>26.250</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>32.667</t>
+          <t>29.245</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>28.846</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>29.787</t>
+          <t>29.545</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -990,7 +978,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>14.734</t>
+          <t>14.201</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1000,14 +988,14 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>26.250</t>
+          <t>29.245</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OR520348</t>
+          <t>OR818251</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1017,42 +1005,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>305</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>14.201</t>
+          <t>20.195</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>31.058</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>34.242</t>
+          <t>31.455</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>29.814</t>
+          <t>28.511</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>29.245</t>
+          <t>28.922</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>28.846</t>
+          <t>29.565</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>29.545</t>
+          <t>34.241</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1062,24 +1045,24 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>14.201</t>
+          <t>20.195</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>29.245</t>
+          <t>29.565</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OR818251</t>
+          <t>AF037230</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1089,37 +1072,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>340</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20.195</t>
+          <t>11.765</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>31.455</t>
+          <t>31.765</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>32.551</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>28.511</t>
+          <t>30.375</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>28.922</t>
+          <t>29.393</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>29.565</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>34.241</t>
+          <t>33.038</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>31.861</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1129,24 +1117,24 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>20.195</t>
+          <t>11.765</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>29.565</t>
+          <t>29.393</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OR825264</t>
+          <t>AY265439</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1156,47 +1144,47 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>402</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13.816</t>
+          <t>15.212</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>28.205</t>
+          <t>30.102</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29.545</t>
+          <t>29.529</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>28.105</t>
+          <t>29.040</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>29.605</t>
+          <t>29.306</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>31.760</t>
+          <t>31.807</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>32.414</t>
+          <t>31.762</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>28.137</t>
+          <t>30.025</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1206,24 +1194,24 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>13.816</t>
+          <t>15.212</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>28.105</t>
+          <t>29.306</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OR825266</t>
+          <t>AY434113</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1233,47 +1221,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>339</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12.500</t>
+          <t>12.941</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>28.413</t>
+          <t>31.871</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>31.061</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>29.582</t>
+          <t>30.792</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>29.276</t>
+          <t>30.990</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>29.897</t>
+          <t>33.041</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>31.803</t>
+          <t>30.284</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>26.996</t>
+          <t>30.579</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1283,24 +1266,24 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>12.500</t>
+          <t>12.941</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>26.996</t>
+          <t>30.792</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OR825270</t>
+          <t>AY632152</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1310,47 +1293,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>377</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>13.158</t>
+          <t>12.997</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>28.205</t>
+          <t>29.973</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>28.409</t>
+          <t>30.159</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>29.260</t>
+          <t>29.101</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>28.618</t>
+          <t>28.912</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>31.064</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>32.941</t>
+          <t>31.481</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>27.757</t>
+          <t>28.756</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1360,24 +1338,24 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>13.158</t>
+          <t>12.997</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>28.618</t>
+          <t>28.756</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OR825280</t>
+          <t>JQ318450</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1387,47 +1365,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>340</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>14.474</t>
+          <t>16.471</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28.571</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>29.434</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>30.000</t>
+          <t>32.824</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>28.852</t>
+          <t>27.090</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>29.817</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>33.443</t>
+          <t>31.579</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>28.897</t>
+          <t>30.268</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1437,7 +1400,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>14.474</t>
+          <t>16.471</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1447,14 +1410,14 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>28.852</t>
+          <t>27.090</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OR825282</t>
+          <t>JQ318452</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1464,42 +1427,47 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>340</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>14.474</t>
+          <t>12.353</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29.720</t>
+          <t>32.647</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>28.302</t>
+          <t>32.258</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>29.677</t>
+          <t>30.717</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>28.197</t>
+          <t>29.167</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>29.817</t>
+          <t>31.858</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>33.569</t>
+          <t>31.230</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>29.134</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1509,7 +1477,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>14.474</t>
+          <t>12.353</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1519,14 +1487,14 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>28.197</t>
+          <t>29.167</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AF037230</t>
+          <t>JQ318462</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1544,29 +1512,19 @@
           <t>11.765</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>31.765</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>32.551</t>
+          <t>33.431</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>30.375</t>
+          <t>30.137</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>29.393</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>33.038</t>
+          <t>28.662</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1574,6 +1532,11 @@
           <t>31.861</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>29.921</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>1</t>
@@ -1591,14 +1554,14 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>29.393</t>
+          <t>28.662</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AY265439</t>
+          <t>JQ318495</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1608,47 +1571,42 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>339</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>15.212</t>
+          <t>14.118</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>30.102</t>
+          <t>32.456</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>29.529</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>29.040</t>
+          <t>32.551</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>29.306</t>
+          <t>31.410</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>31.807</t>
+          <t>33.918</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>31.762</t>
+          <t>31.861</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>30.025</t>
+          <t>33.058</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1658,7 +1616,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>15.212</t>
+          <t>14.118</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1668,14 +1626,14 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>29.306</t>
+          <t>31.410</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AY434113</t>
+          <t>JQ679041</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1685,42 +1643,37 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>350</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12.941</t>
+          <t>17.403</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>31.871</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>30.792</t>
+          <t>31.956</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>30.990</t>
+          <t>29.714</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>33.041</t>
+          <t>33.724</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>30.284</t>
+          <t>31.646</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>30.579</t>
+          <t>30.364</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1730,24 +1683,24 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>12.941</t>
+          <t>17.403</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>30.792</t>
+          <t>29.714</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AY632152</t>
+          <t>JQ679042</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1757,42 +1710,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>358</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12.997</t>
+          <t>17.680</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>29.973</t>
+          <t>31.593</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>30.159</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>29.101</t>
+          <t>29.945</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>28.912</t>
+          <t>30.387</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>31.481</t>
+          <t>30.499</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>28.756</t>
+          <t>29.508</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1802,24 +1750,24 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>12.997</t>
+          <t>17.680</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>28.756</t>
+          <t>30.387</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JQ318450</t>
+          <t>JQ679044</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1829,32 +1777,47 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>362</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>16.471</t>
+          <t>16.851</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>32.824</t>
+          <t>28.297</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>28.881</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>31.287</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>27.090</t>
+          <t>28.453</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>31.579</t>
+          <t>32.845</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>30.904</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>30.268</t>
+          <t>31.285</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1864,7 +1827,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>16.471</t>
+          <t>16.851</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1874,14 +1837,14 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>27.090</t>
+          <t>28.453</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JQ318452</t>
+          <t>JQ679045</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1891,47 +1854,47 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>362</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>12.353</t>
+          <t>18.232</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>32.647</t>
+          <t>28.804</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>32.258</t>
+          <t>30.220</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>30.717</t>
+          <t>32.754</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>29.167</t>
+          <t>27.879</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>31.858</t>
+          <t>33.138</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>31.230</t>
+          <t>30.792</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>29.134</t>
+          <t>29.365</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1941,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>12.353</t>
+          <t>18.232</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1951,14 +1914,14 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>29.167</t>
+          <t>27.879</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JQ318462</t>
+          <t>JQ679049</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1968,37 +1931,47 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>362</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11.765</t>
+          <t>14.917</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>26.997</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>33.431</t>
+          <t>28.685</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>30.137</t>
+          <t>30.702</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>28.662</t>
+          <t>27.273</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>32.845</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>31.861</t>
+          <t>29.878</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>29.921</t>
+          <t>29.052</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2008,24 +1981,24 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>11.765</t>
+          <t>14.917</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>28.662</t>
+          <t>26.997</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JQ318495</t>
+          <t>JQ679050</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2035,42 +2008,47 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>362</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>14.118</t>
+          <t>14.365</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>32.456</t>
+          <t>27.348</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>32.551</t>
+          <t>27.755</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>29.942</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>31.410</t>
+          <t>29.006</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>33.918</t>
+          <t>30.495</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>31.861</t>
+          <t>28.500</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>33.058</t>
+          <t>31.044</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2080,24 +2058,24 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>14.118</t>
+          <t>14.365</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>31.410</t>
+          <t>27.348</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JQ679041</t>
+          <t>JQ679065</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2107,37 +2085,47 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>362</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>17.403</t>
+          <t>12.707</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>31.956</t>
+          <t>30.110</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>31.680</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>29.275</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>29.714</t>
+          <t>29.558</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>33.724</t>
+          <t>30.058</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>31.646</t>
+          <t>32.416</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>30.364</t>
+          <t>30.041</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2147,7 +2135,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>17.403</t>
+          <t>12.707</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2157,14 +2145,14 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>29.714</t>
+          <t>29.558</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JQ679042</t>
+          <t>KM213544</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2174,37 +2162,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>298</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>17.680</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>31.593</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>29.945</t>
+          <t>21.254</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>31.250</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>30.387</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>30.499</t>
+          <t>31.095</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>29.508</t>
+          <t>33.796</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2214,7 +2192,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>17.680</t>
+          <t>21.254</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2224,14 +2202,14 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>30.387</t>
+          <t>31.095</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JQ679044</t>
+          <t>KM213558</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2241,47 +2219,37 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>291</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>16.851</t>
+          <t>18.707</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>28.297</t>
+          <t>29.293</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>28.881</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>31.287</t>
+          <t>30.189</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>28.453</t>
+          <t>28.070</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>32.845</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>30.904</t>
+          <t>30.396</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>31.285</t>
+          <t>26.168</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2291,7 +2259,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>16.851</t>
+          <t>18.707</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2301,14 +2269,14 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>28.453</t>
+          <t>28.070</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JQ679045</t>
+          <t>KY627918</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2318,47 +2286,47 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>347</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>18.232</t>
+          <t>15.493</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>28.804</t>
+          <t>29.268</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>30.220</t>
+          <t>28.674</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>32.754</t>
+          <t>30.960</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>27.879</t>
+          <t>27.941</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>33.138</t>
+          <t>31.373</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>30.792</t>
+          <t>32.486</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>29.365</t>
+          <t>26.990</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2368,7 +2336,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>18.232</t>
+          <t>15.493</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2378,14 +2346,14 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>27.879</t>
+          <t>27.941</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JQ679047</t>
+          <t>L48495</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2395,47 +2363,42 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>326</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>13.812</t>
+          <t>15.951</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>29.282</t>
+          <t>31.529</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>28.689</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>31.287</t>
+          <t>32.808</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>29.006</t>
+          <t>29.703</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>32.970</t>
+          <t>31.489</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>31.307</t>
+          <t>31.937</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>26.070</t>
+          <t>28.800</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2445,7 +2408,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>13.812</t>
+          <t>15.951</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2454,510 +2417,6 @@
         </is>
       </c>
       <c r="O28" t="inlineStr">
-        <is>
-          <t>29.006</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>JQ679049</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1L</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>14.917</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>26.997</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>28.685</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>30.702</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>27.273</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>32.845</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>29.878</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>29.052</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>14.917</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>26.997</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>JQ679050</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1L</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>14.365</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>27.348</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>27.755</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>29.942</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>29.006</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>30.495</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>28.500</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>31.044</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>14.365</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>27.348</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>JQ679065</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1L</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>12.707</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>30.110</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>31.680</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>29.275</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>29.558</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>30.058</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>32.416</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>30.041</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>12.707</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>29.558</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>KM213544</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1L</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>21.254</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>31.250</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>31.095</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>33.796</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>21.254</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>31.095</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>KM213558</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1L</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>18.707</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>29.293</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>30.189</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>28.070</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>30.396</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>26.168</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>18.707</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>28.070</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>KY627918</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1L</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>15.493</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>29.268</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>28.674</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>30.960</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>27.941</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>31.373</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>32.486</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>26.990</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>15.493</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>27.941</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>L48495</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1L</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>15.951</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>31.529</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>32.808</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>29.703</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>31.489</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>31.937</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>28.800</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>15.951</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
         <is>
           <t>29.703</t>
         </is>
@@ -3303,7 +2762,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MN895099</t>
+          <t>MT151093</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3313,7 +2772,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>314</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3323,149 +2782,149 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12.812</t>
+          <t>15.789</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12.812</t>
+          <t>15.789</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>13.681</t>
+          <t>19.142</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>13.681</t>
+          <t>19.142</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13.438</t>
+          <t>14.013</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13.438</t>
+          <t>14.013</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.047</t>
+          <t>15.789</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16.301</t>
+          <t>17.881</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>16.301</t>
+          <t>17.881</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>15.938</t>
+          <t>18.812</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>15.938</t>
+          <t>18.812</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>19.688</t>
+          <t>18.092</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>19.688</t>
+          <t>18.092</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>14.420</t>
+          <t>17.162</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>15.938</t>
+          <t>18.874</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>13.750</t>
+          <t>18.750</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>3.750</t>
+          <t>16.825</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3.750</t>
+          <t>16.825</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>13.333</t>
+          <t>18.874</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>13.333</t>
+          <t>18.874</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>13.480</t>
+          <t>18.092</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.480</t>
+          <t>18.092</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>13.125</t>
+          <t>12.739</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13.125</t>
+          <t>12.739</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1l</t>
+          <t>1o</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3.750</t>
+          <t>12.739</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1a</t>
+          <t>1c</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>12.812</t>
+          <t>14.013</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MT151093</t>
+          <t>MK962423</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3475,7 +2934,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>357</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3485,149 +2944,149 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15.789</t>
+          <t>15.686</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>15.789</t>
+          <t>15.686</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>19.142</t>
+          <t>19.328</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>19.142</t>
+          <t>19.328</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14.013</t>
+          <t>19.608</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14.013</t>
+          <t>19.608</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>15.789</t>
+          <t>20.448</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>17.881</t>
+          <t>19.608</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>17.881</t>
+          <t>19.608</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>18.812</t>
+          <t>20.168</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>18.812</t>
+          <t>20.168</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>18.092</t>
+          <t>23.249</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>18.092</t>
+          <t>23.249</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>17.162</t>
+          <t>21.008</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>18.874</t>
+          <t>18.207</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>18.750</t>
+          <t>17.367</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>16.825</t>
+          <t>17.927</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>16.825</t>
+          <t>17.927</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>18.874</t>
+          <t>16.997</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>18.874</t>
+          <t>16.997</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>18.092</t>
+          <t>16.854</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18.092</t>
+          <t>16.854</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>12.739</t>
+          <t>19.328</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12.739</t>
+          <t>19.328</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>1o</t>
+          <t>1a</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>12.739</t>
+          <t>15.686</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1c</t>
+          <t>1n</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>14.013</t>
+          <t>16.854</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MK962423</t>
+          <t>EF115981</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3637,7 +3096,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>340</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3647,149 +3106,149 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15.686</t>
+          <t>11.799</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>15.686</t>
+          <t>11.799</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19.328</t>
+          <t>18.879</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>19.328</t>
+          <t>18.879</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>19.608</t>
+          <t>15.929</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>19.608</t>
+          <t>15.929</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20.448</t>
+          <t>18.879</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>19.608</t>
+          <t>15.929</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>19.608</t>
+          <t>15.929</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>20.168</t>
+          <t>14.749</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>20.168</t>
+          <t>14.749</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>23.249</t>
+          <t>21.006</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>23.249</t>
+          <t>21.006</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>21.008</t>
+          <t>18.935</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>18.207</t>
+          <t>14.454</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>17.367</t>
+          <t>15.976</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.927</t>
+          <t>12.389</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>17.927</t>
+          <t>12.389</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>16.997</t>
+          <t>11.765</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>16.997</t>
+          <t>11.765</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>16.854</t>
+          <t>14.118</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16.854</t>
+          <t>14.118</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>19.328</t>
+          <t>16.814</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19.328</t>
+          <t>16.814</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
+          <t>1m</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>11.765</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>15.686</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>1n</t>
-        </is>
-      </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>16.854</t>
+          <t>11.799</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EF115981</t>
+          <t>EF115985</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3809,149 +3268,149 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11.799</t>
+          <t>15.294</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11.799</t>
+          <t>15.294</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>18.879</t>
+          <t>20.882</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>18.879</t>
+          <t>20.882</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15.929</t>
+          <t>17.647</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15.929</t>
+          <t>17.647</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>18.879</t>
+          <t>22.941</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>15.929</t>
+          <t>18.824</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>15.929</t>
+          <t>18.824</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>19.706</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>19.706</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>22.781</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>22.781</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>19.505</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>15.882</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>14.749</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>14.749</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>21.006</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>21.006</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>18.935</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>14.454</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>15.976</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>12.389</t>
+          <t>14.412</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>12.389</t>
+          <t>14.412</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>11.765</t>
+          <t>15.294</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>11.765</t>
+          <t>15.294</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>14.118</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14.118</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>16.814</t>
+          <t>16.765</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16.814</t>
+          <t>16.765</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>1n</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>11.765</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1a</t>
+          <t>1l</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>11.799</t>
+          <t>14.412</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EF115985</t>
+          <t>OR477052</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3961,7 +3420,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>317</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3971,132 +3430,132 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15.294</t>
+          <t>14.826</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>15.294</t>
+          <t>14.826</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20.882</t>
+          <t>17.555</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.882</t>
+          <t>17.555</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>17.647</t>
+          <t>14.371</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>17.647</t>
+          <t>14.371</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>22.941</t>
+          <t>12.934</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>18.824</t>
+          <t>15.457</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>18.824</t>
+          <t>15.457</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>19.706</t>
+          <t>17.035</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>19.706</t>
+          <t>17.035</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>22.781</t>
+          <t>18.495</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>22.781</t>
+          <t>18.495</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>19.505</t>
+          <t>13.982</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>15.882</t>
+          <t>17.964</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>14.749</t>
+          <t>15.868</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>14.412</t>
+          <t>14.371</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>14.412</t>
+          <t>14.371</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>15.294</t>
+          <t>16.301</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>15.294</t>
+          <t>16.301</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>13.565</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>13.565</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>16.765</t>
+          <t>14.970</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16.765</t>
+          <t>14.970</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1n</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>12.934</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -4106,14 +3565,14 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>14.412</t>
+          <t>14.371</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OR477052</t>
+          <t>OR520348</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4123,7 +3582,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>338</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4133,149 +3592,149 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14.826</t>
+          <t>14.793</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14.826</t>
+          <t>14.793</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>17.555</t>
+          <t>19.822</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>17.555</t>
+          <t>19.822</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14.371</t>
+          <t>17.751</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14.371</t>
+          <t>17.751</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>12.934</t>
+          <t>18.343</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>15.457</t>
+          <t>19.527</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>15.457</t>
+          <t>19.527</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>17.035</t>
+          <t>19.231</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>17.035</t>
+          <t>19.231</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>18.495</t>
+          <t>21.006</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>18.495</t>
+          <t>21.006</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>13.982</t>
+          <t>18.047</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>17.964</t>
+          <t>15.976</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>15.868</t>
+          <t>18.047</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>14.371</t>
+          <t>14.793</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>14.371</t>
+          <t>14.793</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>16.301</t>
+          <t>14.497</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>16.301</t>
+          <t>14.497</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>13.565</t>
+          <t>15.951</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13.565</t>
+          <t>15.951</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>14.970</t>
+          <t>6.213</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14.970</t>
+          <t>6.213</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>1o</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>12.934</t>
+          <t>6.213</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1l</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>14.371</t>
+          <t>14.497</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OR520348</t>
+          <t>OR818251</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4285,7 +3744,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>305</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4295,122 +3754,122 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14.793</t>
+          <t>20.847</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14.793</t>
+          <t>20.847</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>19.822</t>
+          <t>19.366</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>19.822</t>
+          <t>19.366</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>17.751</t>
+          <t>20.521</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17.751</t>
+          <t>20.521</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>18.343</t>
+          <t>19.935</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>19.527</t>
+          <t>19.608</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>19.527</t>
+          <t>19.608</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>19.231</t>
+          <t>20.455</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>19.231</t>
+          <t>20.455</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>21.006</t>
+          <t>20.463</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>21.006</t>
+          <t>20.463</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>18.047</t>
+          <t>19.608</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>15.976</t>
+          <t>19.935</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>18.047</t>
+          <t>17.761</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>14.793</t>
+          <t>20.261</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>14.793</t>
+          <t>20.261</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>14.497</t>
+          <t>20.261</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>14.497</t>
+          <t>20.261</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>15.951</t>
+          <t>17.442</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15.951</t>
+          <t>17.442</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>6.213</t>
+          <t>16.393</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>6.213</t>
+          <t>16.393</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4420,24 +3879,24 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6.213</t>
+          <t>16.393</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>1i</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>14.497</t>
+          <t>19.608</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OR818251</t>
+          <t>AF037230</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4447,7 +3906,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>340</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4457,149 +3916,149 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20.847</t>
+          <t>11.471</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.847</t>
+          <t>11.471</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>19.366</t>
+          <t>18.619</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>19.366</t>
+          <t>18.619</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20.521</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>20.521</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>19.935</t>
+          <t>20.882</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>19.608</t>
+          <t>17.353</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>19.608</t>
+          <t>17.353</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>20.455</t>
+          <t>14.706</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>20.455</t>
+          <t>14.706</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>20.463</t>
+          <t>22.781</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>20.463</t>
+          <t>22.781</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>19.608</t>
+          <t>17.718</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>19.935</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>17.761</t>
+          <t>13.274</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>20.261</t>
+          <t>14.412</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>20.261</t>
+          <t>14.412</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>20.261</t>
+          <t>12.059</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>20.261</t>
+          <t>12.059</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>17.442</t>
+          <t>11.504</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17.442</t>
+          <t>11.504</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>16.393</t>
+          <t>18.235</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16.393</t>
+          <t>18.235</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>1o</t>
+          <t>1a</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>16.393</t>
+          <t>11.471</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1i</t>
+          <t>1n</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>19.608</t>
+          <t>11.504</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OR825264</t>
+          <t>AY265439</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4609,7 +4068,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>402</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4619,149 +4078,149 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13.158</t>
+          <t>15.960</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>13.158</t>
+          <t>15.960</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>15.789</t>
+          <t>14.925</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>15.789</t>
+          <t>14.925</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15.132</t>
+          <t>16.459</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15.132</t>
+          <t>16.459</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>15.924</t>
+          <t>16.708</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>17.105</t>
+          <t>16.923</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>17.105</t>
+          <t>16.923</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>16.447</t>
+          <t>18.204</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>16.447</t>
+          <t>18.204</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>19.737</t>
+          <t>18.750</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>19.737</t>
+          <t>18.750</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>15.789</t>
+          <t>15.090</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>14.803</t>
+          <t>17.207</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>14.145</t>
+          <t>16.958</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>4.605</t>
+          <t>15.960</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>4.605</t>
+          <t>15.960</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>12.040</t>
+          <t>16.000</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>12.040</t>
+          <t>16.000</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>13.487</t>
+          <t>17.207</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13.487</t>
+          <t>17.207</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>15.132</t>
+          <t>16.708</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15.132</t>
+          <t>16.708</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1l</t>
+          <t>1b</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4.605</t>
+          <t>14.925</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>1i</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>12.040</t>
+          <t>15.090</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OR825266</t>
+          <t>AY434113</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4771,7 +4230,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>339</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4781,149 +4240,149 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11.974</t>
+          <t>12.647</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>11.974</t>
+          <t>12.647</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>14.145</t>
+          <t>19.412</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>14.145</t>
+          <t>19.412</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>13.826</t>
+          <t>17.941</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13.826</t>
+          <t>17.941</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>14.968</t>
+          <t>19.706</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>16.447</t>
+          <t>17.647</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>16.447</t>
+          <t>17.647</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>16.447</t>
+          <t>16.765</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>16.447</t>
+          <t>16.765</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>19.094</t>
+          <t>19.822</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>19.094</t>
+          <t>19.822</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>14.474</t>
+          <t>17.073</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>14.803</t>
+          <t>10.882</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>14.887</t>
+          <t>5.310</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>3.859</t>
+          <t>13.824</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3.859</t>
+          <t>13.824</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>10.855</t>
+          <t>11.799</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>10.855</t>
+          <t>11.799</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>13.916</t>
+          <t>12.353</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13.916</t>
+          <t>12.353</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>13.871</t>
+          <t>17.941</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13.871</t>
+          <t>17.941</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1l</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3.859</t>
+          <t>5.310</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>1j</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>10.855</t>
+          <t>10.882</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OR825270</t>
+          <t>AY632152</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4933,7 +4392,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>377</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4943,132 +4402,132 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13.269</t>
+          <t>13.528</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13.269</t>
+          <t>13.528</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>14.803</t>
+          <t>15.831</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>14.803</t>
+          <t>15.831</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>14.968</t>
+          <t>11.406</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14.968</t>
+          <t>11.406</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>16.026</t>
+          <t>14.660</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>17.105</t>
+          <t>15.650</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>17.105</t>
+          <t>15.650</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>17.434</t>
+          <t>16.976</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>17.434</t>
+          <t>16.976</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>20.066</t>
+          <t>17.507</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>20.066</t>
+          <t>17.507</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>15.132</t>
+          <t>15.040</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>15.132</t>
+          <t>15.119</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>14.563</t>
+          <t>17.507</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>5.449</t>
+          <t>12.467</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>5.449</t>
+          <t>12.467</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>12.829</t>
+          <t>16.138</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>12.829</t>
+          <t>16.138</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>12.945</t>
+          <t>15.650</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12.945</t>
+          <t>15.650</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>13.208</t>
+          <t>11.671</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13.208</t>
+          <t>11.671</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>1l</t>
+          <t>1c</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>5.449</t>
+          <t>11.406</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -5078,14 +4537,14 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>13.208</t>
+          <t>11.671</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OR825280</t>
+          <t>JQ318450</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5095,7 +4554,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>340</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5105,149 +4564,149 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13.916</t>
+          <t>15.294</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.916</t>
+          <t>15.294</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>16.776</t>
+          <t>19.355</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>16.776</t>
+          <t>19.355</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15.434</t>
+          <t>14.706</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>15.434</t>
+          <t>14.706</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>16.026</t>
+          <t>19.825</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17.105</t>
+          <t>16.765</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>17.105</t>
+          <t>16.765</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>17.434</t>
+          <t>19.355</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>17.434</t>
+          <t>19.355</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>19.417</t>
+          <t>20.118</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>19.417</t>
+          <t>20.118</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>16.118</t>
+          <t>17.994</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>15.132</t>
+          <t>18.235</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>14.887</t>
+          <t>16.224</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>3.526</t>
+          <t>14.706</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>3.526</t>
+          <t>14.706</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>11.842</t>
+          <t>16.224</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>11.842</t>
+          <t>16.224</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>13.681</t>
+          <t>14.749</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13.681</t>
+          <t>14.749</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>13.871</t>
+          <t>13.235</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13.871</t>
+          <t>13.235</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
+          <t>1o</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>13.235</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
           <t>1l</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>3.526</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>1m</t>
-        </is>
-      </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>11.842</t>
+          <t>14.706</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OR825282</t>
+          <t>JQ318452</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5257,7 +4716,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>340</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5267,149 +4726,149 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13.916</t>
+          <t>11.471</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>13.916</t>
+          <t>11.471</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17.434</t>
+          <t>19.219</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17.434</t>
+          <t>19.219</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>16.077</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>16.077</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>15.064</t>
+          <t>20.294</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>17.105</t>
+          <t>16.176</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>17.105</t>
+          <t>16.176</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>17.763</t>
+          <t>15.294</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>17.763</t>
+          <t>15.294</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>19.417</t>
+          <t>22.189</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>19.417</t>
+          <t>22.189</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>15.461</t>
+          <t>17.417</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>15.132</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>14.563</t>
+          <t>11.799</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>6.984</t>
+          <t>14.706</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>6.984</t>
+          <t>14.706</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>13.487</t>
+          <t>10.588</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>13.487</t>
+          <t>10.588</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>14.007</t>
+          <t>10.914</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14.007</t>
+          <t>10.914</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>12.581</t>
+          <t>17.353</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12.581</t>
+          <t>17.353</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>1l</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>6.984</t>
+          <t>10.588</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1o</t>
+          <t>1n</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>12.581</t>
+          <t>10.914</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AF037230</t>
+          <t>JQ318462</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5439,139 +4898,139 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>18.619</t>
+          <t>18.919</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>18.619</t>
+          <t>18.919</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>18.529</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>18.529</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>20.000</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>20.000</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>20.882</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>17.353</t>
+          <t>17.941</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>17.353</t>
+          <t>17.941</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>14.706</t>
+          <t>15.588</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>14.706</t>
+          <t>15.588</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>22.781</t>
+          <t>23.077</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>22.781</t>
+          <t>23.077</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>17.718</t>
+          <t>16.817</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
+          <t>14.118</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>12.684</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>15.000</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>13.274</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>14.412</t>
-        </is>
-      </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>14.412</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>12.059</t>
+          <t>11.471</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>12.059</t>
+          <t>11.471</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>11.504</t>
+          <t>12.389</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11.504</t>
+          <t>12.389</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>18.235</t>
+          <t>17.059</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18.235</t>
+          <t>17.059</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
+          <t>1m</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>11.471</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AF16" t="inlineStr">
         <is>
           <t>11.471</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>1n</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>11.504</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AY265439</t>
+          <t>JQ318495</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5581,7 +5040,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>339</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5591,149 +5050,149 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15.960</t>
+          <t>14.118</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>15.960</t>
+          <t>14.118</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14.925</t>
+          <t>20.294</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>14.925</t>
+          <t>20.294</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>16.459</t>
+          <t>19.412</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>16.459</t>
+          <t>19.412</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>16.708</t>
+          <t>20.882</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>16.923</t>
+          <t>18.529</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>16.923</t>
+          <t>18.529</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>18.204</t>
+          <t>17.059</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>18.204</t>
+          <t>17.059</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>18.750</t>
+          <t>20.414</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>18.750</t>
+          <t>20.414</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>15.090</t>
+          <t>19.512</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>17.207</t>
+          <t>13.529</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>16.958</t>
+          <t>6.490</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>15.960</t>
+          <t>15.588</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>15.960</t>
+          <t>15.588</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>16.000</t>
+          <t>12.647</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>16.000</t>
+          <t>12.647</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>17.207</t>
+          <t>13.864</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17.207</t>
+          <t>13.864</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>16.708</t>
+          <t>19.412</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16.708</t>
+          <t>19.412</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>1b</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>14.925</t>
+          <t>6.490</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1i</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>15.090</t>
+          <t>12.647</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AY434113</t>
+          <t>JQ679041</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5743,7 +5202,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>350</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5753,149 +5212,149 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12.647</t>
+          <t>16.575</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>12.647</t>
+          <t>16.575</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19.412</t>
+          <t>19.714</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>19.412</t>
+          <t>19.714</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>17.941</t>
+          <t>17.714</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>17.941</t>
+          <t>17.714</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>19.706</t>
+          <t>20.718</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>17.647</t>
+          <t>17.714</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>17.647</t>
+          <t>17.714</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>16.765</t>
+          <t>18.571</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>16.765</t>
+          <t>18.571</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>19.822</t>
+          <t>21.547</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>19.822</t>
+          <t>21.547</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>17.073</t>
+          <t>19.890</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>10.882</t>
+          <t>14.286</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>5.310</t>
+          <t>15.714</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>13.824</t>
+          <t>14.571</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>13.824</t>
+          <t>14.571</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>11.799</t>
+          <t>16.000</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>11.799</t>
+          <t>16.000</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>12.353</t>
+          <t>15.029</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12.353</t>
+          <t>15.029</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>17.941</t>
+          <t>15.143</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17.941</t>
+          <t>15.143</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>1j</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>5.310</t>
+          <t>14.286</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1j</t>
+          <t>1l</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>10.882</t>
+          <t>14.571</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AY632152</t>
+          <t>JQ679042</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5905,7 +5364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>358</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5915,149 +5374,149 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.528</t>
+          <t>16.298</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>13.528</t>
+          <t>16.298</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>15.831</t>
+          <t>19.061</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>15.831</t>
+          <t>19.061</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>11.406</t>
+          <t>17.956</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>11.406</t>
+          <t>17.956</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>14.660</t>
+          <t>18.508</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>15.650</t>
+          <t>20.718</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>15.650</t>
+          <t>20.718</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>16.976</t>
+          <t>21.547</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>16.976</t>
+          <t>21.547</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>17.507</t>
+          <t>19.613</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>17.507</t>
+          <t>19.613</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>15.040</t>
+          <t>20.166</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>15.119</t>
+          <t>17.127</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>17.507</t>
+          <t>17.403</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>12.467</t>
+          <t>16.298</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>12.467</t>
+          <t>16.298</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>16.138</t>
+          <t>15.922</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>16.138</t>
+          <t>15.922</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>15.650</t>
+          <t>18.436</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15.650</t>
+          <t>18.436</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>11.671</t>
+          <t>18.508</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11.671</t>
+          <t>18.508</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1c</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>11.406</t>
+          <t>15.922</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1o</t>
+          <t>1l</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>11.671</t>
+          <t>16.298</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JQ318450</t>
+          <t>JQ679044</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6067,7 +5526,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>362</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6077,122 +5536,122 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>15.294</t>
+          <t>16.851</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>15.294</t>
+          <t>16.851</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>19.355</t>
+          <t>18.508</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>19.355</t>
+          <t>18.508</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>14.706</t>
+          <t>17.127</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14.706</t>
+          <t>17.127</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>19.825</t>
+          <t>17.956</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>16.765</t>
+          <t>17.680</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>16.765</t>
+          <t>17.680</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>19.355</t>
+          <t>17.956</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>19.355</t>
+          <t>17.956</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>20.118</t>
+          <t>19.890</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>20.118</t>
+          <t>19.890</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>17.994</t>
+          <t>17.680</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>18.235</t>
+          <t>18.232</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>16.224</t>
+          <t>18.232</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>14.706</t>
+          <t>16.851</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>14.706</t>
+          <t>16.851</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>16.224</t>
+          <t>17.598</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>16.224</t>
+          <t>17.598</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>14.749</t>
+          <t>17.956</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14.749</t>
+          <t>17.956</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>13.235</t>
+          <t>16.298</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13.235</t>
+          <t>16.298</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -6202,7 +5661,7 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>13.235</t>
+          <t>16.298</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
@@ -6212,14 +5671,14 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>14.706</t>
+          <t>16.851</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JQ318452</t>
+          <t>JQ679045</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6229,7 +5688,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>362</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -6239,149 +5698,149 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>11.471</t>
+          <t>18.232</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>11.471</t>
+          <t>18.232</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>19.219</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>19.219</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>19.890</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>19.890</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>20.294</t>
+          <t>19.830</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>16.176</t>
+          <t>19.890</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>16.176</t>
+          <t>19.890</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>15.294</t>
+          <t>19.710</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>15.294</t>
+          <t>19.710</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>22.189</t>
+          <t>21.408</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>22.189</t>
+          <t>21.408</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>17.417</t>
+          <t>18.605</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>17.680</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>11.799</t>
+          <t>16.851</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>14.706</t>
+          <t>17.889</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>14.706</t>
+          <t>17.889</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>10.588</t>
+          <t>17.403</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>10.588</t>
+          <t>17.403</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>10.914</t>
+          <t>18.106</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10.914</t>
+          <t>18.106</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>17.353</t>
+          <t>17.403</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17.353</t>
+          <t>17.403</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>10.588</t>
+          <t>16.851</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1n</t>
+          <t>1o</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>10.914</t>
+          <t>17.403</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JQ318462</t>
+          <t>JQ679049</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6391,7 +5850,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>362</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6401,149 +5860,149 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11.471</t>
+          <t>14.641</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>11.471</t>
+          <t>14.641</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>18.919</t>
+          <t>17.127</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>18.919</t>
+          <t>17.127</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>18.529</t>
+          <t>14.088</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>18.529</t>
+          <t>14.088</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>16.851</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>17.941</t>
+          <t>17.956</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>17.941</t>
+          <t>17.956</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>15.588</t>
+          <t>16.851</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>15.588</t>
+          <t>16.851</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>23.077</t>
+          <t>18.785</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>23.077</t>
+          <t>18.785</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>16.817</t>
+          <t>14.365</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>14.118</t>
+          <t>17.956</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>12.684</t>
+          <t>17.956</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>14.641</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>14.641</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>11.471</t>
+          <t>16.298</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>11.471</t>
+          <t>16.298</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>12.389</t>
+          <t>16.480</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12.389</t>
+          <t>16.480</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>17.059</t>
+          <t>15.470</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17.059</t>
+          <t>15.470</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>1c</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>11.471</t>
+          <t>14.088</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1a</t>
+          <t>1i</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>11.471</t>
+          <t>14.365</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JQ318495</t>
+          <t>JQ679050</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6553,7 +6012,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>362</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -6563,149 +6022,149 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>14.118</t>
+          <t>14.365</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14.118</t>
+          <t>14.365</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20.294</t>
+          <t>15.746</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>20.294</t>
+          <t>15.746</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>19.412</t>
+          <t>14.365</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>19.412</t>
+          <t>14.365</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>20.882</t>
+          <t>14.641</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>18.529</t>
+          <t>17.680</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>18.529</t>
+          <t>17.680</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>17.059</t>
+          <t>16.298</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>17.059</t>
+          <t>16.298</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>20.414</t>
+          <t>19.832</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>20.414</t>
+          <t>19.832</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>19.512</t>
+          <t>15.297</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>13.529</t>
+          <t>18.232</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>6.490</t>
+          <t>18.508</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>15.588</t>
+          <t>14.641</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>15.588</t>
+          <t>14.641</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>12.647</t>
+          <t>16.022</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>12.647</t>
+          <t>16.022</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>13.864</t>
+          <t>17.680</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13.864</t>
+          <t>17.680</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>19.412</t>
+          <t>16.022</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19.412</t>
+          <t>16.022</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>6.490</t>
+          <t>14.641</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>1c</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>12.647</t>
+          <t>14.365</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JQ679041</t>
+          <t>JQ679065</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6715,7 +6174,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>362</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -6725,132 +6184,132 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16.575</t>
+          <t>13.536</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>16.575</t>
+          <t>13.536</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>19.714</t>
+          <t>16.298</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>19.714</t>
+          <t>16.298</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>17.714</t>
+          <t>12.707</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>17.714</t>
+          <t>12.707</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>20.718</t>
+          <t>17.680</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>17.714</t>
+          <t>18.232</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>17.714</t>
+          <t>18.232</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>18.571</t>
+          <t>19.061</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>18.571</t>
+          <t>19.061</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>21.547</t>
+          <t>18.232</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>21.547</t>
+          <t>18.232</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>19.890</t>
+          <t>15.193</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>14.286</t>
+          <t>14.365</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>15.714</t>
+          <t>15.746</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>14.571</t>
+          <t>12.707</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>14.571</t>
+          <t>12.707</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>16.000</t>
+          <t>15.193</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>16.000</t>
+          <t>15.193</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>15.029</t>
+          <t>16.298</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15.029</t>
+          <t>16.298</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>15.143</t>
+          <t>12.707</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15.143</t>
+          <t>12.707</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>1j</t>
+          <t>1o</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>14.286</t>
+          <t>12.707</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
@@ -6860,14 +6319,14 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>14.571</t>
+          <t>12.707</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JQ679042</t>
+          <t>KM213544</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6877,7 +6336,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>298</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -6887,122 +6346,122 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16.298</t>
+          <t>20.280</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>16.298</t>
+          <t>20.280</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>19.061</t>
+          <t>21.678</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>19.061</t>
+          <t>21.678</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>17.956</t>
+          <t>22.635</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>17.956</t>
+          <t>22.635</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>18.508</t>
+          <t>21.479</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>20.718</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>20.718</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>21.547</t>
+          <t>22.807</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>21.547</t>
+          <t>22.807</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>19.613</t>
+          <t>22.569</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>19.613</t>
+          <t>22.569</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>20.166</t>
+          <t>23.986</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>17.127</t>
+          <t>18.243</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>17.403</t>
+          <t>20.401</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>16.298</t>
+          <t>19.580</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>16.298</t>
+          <t>19.580</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>15.922</t>
+          <t>18.121</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>15.922</t>
+          <t>18.121</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>18.436</t>
+          <t>19.799</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18.436</t>
+          <t>19.799</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>18.508</t>
+          <t>21.356</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18.508</t>
+          <t>21.356</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -7012,24 +6471,24 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>15.922</t>
+          <t>18.121</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>1l</t>
+          <t>1j</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>16.298</t>
+          <t>18.243</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JQ679044</t>
+          <t>KM213558</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -7039,7 +6498,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>291</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -7049,132 +6508,132 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16.851</t>
+          <t>18.707</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>16.851</t>
+          <t>18.707</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>18.508</t>
+          <t>17.230</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>18.508</t>
+          <t>17.230</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>17.127</t>
+          <t>17.193</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>17.127</t>
+          <t>17.193</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>17.956</t>
+          <t>15.464</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>17.680</t>
+          <t>18.919</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>17.680</t>
+          <t>18.919</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>17.956</t>
+          <t>19.257</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>17.956</t>
+          <t>19.257</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>19.890</t>
+          <t>17.007</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>19.890</t>
+          <t>17.007</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>17.680</t>
+          <t>17.869</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>18.232</t>
+          <t>17.123</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>18.232</t>
+          <t>19.113</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>16.851</t>
+          <t>15.464</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>16.851</t>
+          <t>15.464</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>17.598</t>
+          <t>17.869</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>17.598</t>
+          <t>17.869</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>17.956</t>
+          <t>18.493</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17.956</t>
+          <t>18.493</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>16.298</t>
+          <t>15.141</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16.298</t>
+          <t>15.141</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1o</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>16.298</t>
+          <t>15.464</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
@@ -7184,14 +6643,14 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>16.851</t>
+          <t>15.464</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JQ679045</t>
+          <t>KY627918</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7201,7 +6660,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>347</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -7211,149 +6670,149 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>18.232</t>
+          <t>16.338</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>18.232</t>
+          <t>16.338</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>14.930</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>14.930</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>19.890</t>
+          <t>14.571</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>19.890</t>
+          <t>14.571</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>19.830</t>
+          <t>18.592</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>19.890</t>
+          <t>18.732</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>19.890</t>
+          <t>18.732</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>19.710</t>
+          <t>19.308</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>19.710</t>
+          <t>19.308</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>21.408</t>
+          <t>20.173</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>21.408</t>
+          <t>20.173</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>18.605</t>
+          <t>14.164</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>17.680</t>
+          <t>18.310</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>16.851</t>
+          <t>18.310</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>17.889</t>
+          <t>15.562</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>17.889</t>
+          <t>15.562</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>17.403</t>
+          <t>16.997</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>17.403</t>
+          <t>16.997</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>18.106</t>
+          <t>17.579</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18.106</t>
+          <t>17.579</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>17.403</t>
+          <t>12.392</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17.403</t>
+          <t>12.392</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>1o</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>16.851</t>
+          <t>12.392</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>1o</t>
+          <t>1i</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>17.403</t>
+          <t>14.164</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JQ679047</t>
+          <t>L48495</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7363,7 +6822,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>326</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -7373,2196 +6832,142 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>13.260</t>
+          <t>16.564</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>13.260</t>
+          <t>16.564</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>17.127</t>
+          <t>15.644</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>17.127</t>
+          <t>15.644</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>15.193</t>
+          <t>15.951</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>15.193</t>
+          <t>15.951</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>15.193</t>
+          <t>14.110</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>16.851</t>
+          <t>19.018</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>16.851</t>
+          <t>19.018</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>17.680</t>
+          <t>20.552</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>17.680</t>
+          <t>20.552</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>17.877</t>
+          <t>18.712</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>17.877</t>
+          <t>18.712</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>15.581</t>
+          <t>7.669</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>15.193</t>
+          <t>19.018</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>17.680</t>
+          <t>19.315</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>11.326</t>
+          <t>15.951</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>11.326</t>
+          <t>15.951</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>15.470</t>
+          <t>16.258</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>15.470</t>
+          <t>16.258</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>16.298</t>
+          <t>17.500</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16.298</t>
+          <t>17.500</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>15.193</t>
+          <t>18.098</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15.193</t>
+          <t>18.098</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>1l</t>
+          <t>1i</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>11.326</t>
+          <t>7.669</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>1a</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>13.260</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>JQ679049</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1L</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>14.641</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>14.641</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>17.127</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>17.127</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>14.088</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>14.088</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>16.851</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>17.956</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>17.956</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>16.851</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>16.851</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>18.785</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>18.785</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>14.365</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>17.956</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>17.956</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>14.641</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>14.641</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>16.298</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>16.298</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>16.480</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>16.480</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>15.470</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15.470</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>1c</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>14.088</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>1i</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>14.365</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>JQ679050</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1L</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>14.365</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>14.365</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>15.746</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>15.746</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>14.365</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>14.365</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>14.641</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>17.680</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>17.680</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>16.298</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>16.298</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>19.832</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>19.832</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>15.297</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>18.232</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>18.508</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>14.641</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>14.641</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>16.022</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>16.022</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>17.680</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>17.680</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>16.022</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>16.022</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>14.641</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>1c</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>14.365</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>JQ679065</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1L</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>13.536</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>13.536</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>16.298</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>16.298</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>12.707</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>12.707</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>17.680</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>18.232</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>18.232</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>19.061</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>19.061</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>18.232</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>18.232</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>15.193</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>14.365</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>15.746</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>12.707</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>12.707</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>15.193</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>15.193</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>16.298</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>16.298</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>12.707</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12.707</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>1o</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>12.707</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>1l</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>12.707</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>KM213544</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1L</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>20.280</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>20.280</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>21.678</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>21.678</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>22.635</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>22.635</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>21.479</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>20.000</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>20.000</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>22.807</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>22.807</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>22.569</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>22.569</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>23.986</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>18.243</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>20.401</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>19.580</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>19.580</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>18.121</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>18.121</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>19.799</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>19.799</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>21.356</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>21.356</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>1m</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>18.121</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>1j</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>18.243</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>KM213558</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1L</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>18.707</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>18.707</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>17.230</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>17.230</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>17.193</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>17.193</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>15.464</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>18.919</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>18.919</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>19.257</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>19.257</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>17.007</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>17.007</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>17.869</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>17.123</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>19.113</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>15.464</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>15.464</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>17.869</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>17.869</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>18.493</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>18.493</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>15.141</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15.141</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>15.464</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>1l</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>15.464</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>KY627918</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1L</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>16.338</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>16.338</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>14.930</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>14.930</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>14.571</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>14.571</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>18.592</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>18.732</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>18.732</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>19.308</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>19.308</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>20.173</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>20.173</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>14.164</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>18.310</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>18.310</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>15.562</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>15.562</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>16.997</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>16.997</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>17.579</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>17.579</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>12.392</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12.392</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>1o</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>12.392</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>1i</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>14.164</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>L48495</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1L</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>16.564</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>16.564</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>15.644</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>15.644</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>15.951</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>15.951</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
           <t>14.110</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>19.018</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>19.018</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>20.552</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>20.552</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>18.712</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>18.712</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>7.669</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>19.018</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>19.315</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>15.951</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>15.951</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>16.258</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>16.258</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>17.500</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>17.500</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>18.098</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>18.098</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1i</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>7.669</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>14.110</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype2aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype2aDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Subtype2bDistance</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Subtype2bDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Subtype2cDistance</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Subtype2dDistance</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Subtype2eDistance</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Subtype2fDistance</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Subtype2fDistance</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Subtype2iDistance</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Subtype2jDistance</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Subtype2jDistance</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Subtype2kDistance</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Subtype2lDistance</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Subtype2lDistance</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Subtype2mDistance</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Subtype2mDistance</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Subtype2qDistance</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Subtype2qDistance</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Subtype2rDistance</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Subtype2tDistance</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Subtype2uDistance</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Subtype2vDistance</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype3aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype3bDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Subtype3dDistance</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Subtype3eDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Subtype3gDistance</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Subtype3gDistance</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Subtype3hDistance</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Subtype3iDistance</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Subtype3iDistance</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Subtype3kDistance</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Subtype3kDistance</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype4aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype4bDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Subtype4cDistance</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Subtype4dDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Subtype4dDistance</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Subtype4fDistance</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Subtype4fDistance</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Subtype4gDistance</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Subtype4kDistance</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Subtype4kDistance</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Subtype4lDistance</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Subtype4mDistance</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Subtype4nDistance</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Subtype4oDistance</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Subtype4pDistance</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Subtype4qDistance</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Subtype4rDistance</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Subtype4sDistance</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Subtype4tDistance</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Subtype4vDistance</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Subtype4vDistance</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Subtype4wDistance</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Subtype4wDistance</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype5aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype5bDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype6aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype6aDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Subtype6bDistance</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Subtype6cDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Subtype6dDistance</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Subtype6eDistance</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Subtype6fDistance</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Subtype6gDistance</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Subtype6hDistance</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Subtype6iDistance</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Subtype6jDistance</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Subtype6kDistance</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Subtype6lDistance</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Subtype6mDistance</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Subtype6nDistance</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Subtype6nDistance</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Subtype6oDistance</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Subtype6pDistance</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Subtype6qDistance</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Subtype6rDistance</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Subtype6sDistance</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Subtype6tDistance</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Subtype6tDistance</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Subtype6uDistance</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Subtype6vDistance</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Subtype6vDistance</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Subtype6wDistance</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Subtype6wDistance</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Subtype6xaDistance</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Subtype6xaDistance</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Subtype6xbDistance</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Subtype6xbDistance</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Subtype6xcDistance</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>Subtype6xdDistance</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>Subtype6xdDistance</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>Subtype6xeDistance</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>Subtype6xeDistance</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>Subtype6xfDistance</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>Subtype6xfDistance</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>Subtype6xgDistance</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>Subtype6xgDistance</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>Subtype6xhDistance</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>Subtype6xiDistance</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>Subtype6xiDistance</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>Subtype6xjDistance</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype7aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype7bDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype8aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
         </is>
       </c>
     </row>
